--- a/InputFiles/ICDC/TC13_ICDC_COTC021_FileAssociation-Sample.xlsx
+++ b/InputFiles/ICDC/TC13_ICDC_COTC021_FileAssociation-Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC124FB9-3B2F-B142-BF02-33A4AAD58E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C807680F-5D58-584E-98E4-EE1EB0DA21CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="40760" yWindow="2020" windowWidth="24920" windowHeight="17540" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,6 +64,99 @@
   </si>
   <si>
     <t>TC13_ICDC_COTC021_FileAssociation-Sample_WebData.xlsx</t>
+  </si>
+  <si>
+    <t>SELECT
+    DISTINCT c.case_record_id AS "Case ID",
+    st.clinical_study_designation AS "Study Code",
+    st.clinical_study_type AS "Study Type",
+    dmg.breed AS "Breed",
+    diag.disease_term AS "Diagnosis",
+    diag.stage_of_disease AS "Stage Of Disease",
+    CASE 
+    WHEN dmg.patient_age_at_enrollment = CAST(dmg.patient_age_at_enrollment AS INT) 
+    THEN CAST(CAST(dmg.patient_age_at_enrollment AS INT) AS TEXT)
+    ELSE CAST(dmg.patient_age_at_enrollment AS TEXT)
+END AS "Age", 
+    COALESCE(TRIM(dmg.sex), '') AS "Sex",   
+    COALESCE(dmg.neutered_indicator, '') AS "Neutered Status",  
+    COALESCE(
+         CASE 
+            WHEN dmg.weight = CAST(dmg.weight AS INT) THEN CAST(CAST(ROUND(dmg.weight, 0) AS INT) AS TEXT) 
+            ELSE dmg.weight 
+        END, 
+    '') AS "Weight (kg)",        
+    COALESCE(diag.best_response, '') AS "Response to Treatment",  
+    COALESCE(coh.cohort_description, '') AS "Cohort"  
+FROM 
+    df_case c
+JOIN 
+    df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
+JOIN 
+    df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
+JOIN 
+    df_diagnosis diag ON diag."case.case_record_id" = c.case_record_id
+JOIN 
+    df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
+JOIN 
+    df_program p ON st."program.program_acronym" = p.program_acronym
+JOIN 
+    df_sample smp ON smp."case.case_id" = c.case_record_id
+JOIN 
+    df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
+LEFT JOIN 
+    df_case_file cf ON cf."sample.sample_id" = smp.sample_id
+LEFT JOIN 
+    df_study_file sf ON sf."study.clinical_study_designation" = st.clinical_study_designation
+LEFT JOIN
+   df_cohort coh ON coh.cohort_record_id= c."cohort.cohort_record_id"
+WHERE
+    st.clinical_study_designation = 'COTC021' AND cf."sample.sample_id" LIKE 'COTC021%'
+ORDER BY 
+    c.case_record_id ASC
+LIMIT 100;</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT
+    smp.sample_id AS "Sample ID",
+    c.case_record_id AS "Case ID",
+    COALESCE(dmg.breed, '') AS "Breed",
+    COALESCE(diag.disease_term, '') AS "Diagnosis",
+    COALESCE(smp.sample_site, '') AS "Sample Site",
+    COALESCE(smp.summarized_sample_type, '') AS "Sample Type",
+    COALESCE(smp.specific_sample_pathology, '') AS "Pathology/Morphology",
+    COALESCE(smp.tumor_grade, '') AS "Tumor Grade",
+    COALESCE(smp.sample_chronology, '') AS "Sample Chronology",
+    COALESCE(smp.percentage_tumor, '') AS "Percentage Tumor",
+    COALESCE(smp.necropsy_sample, '') AS "Necropsy Sample",
+    COALESCE(smp.sample_preservation, '') AS "Sample Preservation"
+FROM df_sample smp
+JOIN df_case c
+  ON smp."case.case_id" = c.case_record_id
+JOIN df_study st
+  ON c."study.clinical_study_designation" = st.clinical_study_designation
+JOIN df_program p
+  ON st."program.program_acronym" = p.program_acronym
+JOIN df_publication pub
+  ON pub."study.clinical_study_designation" = st.clinical_study_designation
+JOIN df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
+JOIN df_diagnosis diag  ON diag."case.case_record_id" = c.case_record_id
+JOIN df_enrollment enr  ON enr."case.case_record_id" = c.case_record_id
+LEFT JOIN df_case_file cf
+  ON cf."sample.sample_id" = smp.sample_id
+LEFT JOIN df_study_file sf
+  ON sf."study.clinical_study_designation" = st.clinical_study_designation
+WHERE st.clinical_study_designation = 'COTC021'
+  AND EXISTS (
+      SELECT 1
+      FROM df_sample s2
+      JOIN df_case_file cf2
+        ON cf2."sample.sample_id" = s2.sample_id
+      WHERE s2."case.case_record_id" = c.case_record_id
+        AND cf2."sample.sample_id" LIKE 'COTC021%'
+  )
+ORDER BY smp.sample_id ASC
+LIMIT 100;</t>
   </si>
   <si>
     <t>SELECT DISTINCT
@@ -102,7 +195,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -121,140 +214,6 @@
     st.clinical_study_designation = 'COTC021' AND sf."sample.sample_id" LIKE 'COTC021%'
 ORDER BY 
     sf.file_name ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT
-    DISTINCT c.case_record_id AS "Case ID",
-    st.clinical_study_designation AS "Study Code",
-    st.clinical_study_type AS "Study Type",
-    dmg.breed AS "Breed",
-    diag.disease_term AS "Diagnosis",
-    diag.stage_of_disease AS "Stage Of Disease",
-    CASE 
-    WHEN dmg.patient_age_at_enrollment = CAST(dmg.patient_age_at_enrollment AS INT) 
-    THEN CAST(CAST(dmg.patient_age_at_enrollment AS INT) AS TEXT)
-    ELSE CAST(dmg.patient_age_at_enrollment AS TEXT)
-END AS "Age", 
-    COALESCE(TRIM(dmg.sex), '') AS "Sex",   
-    COALESCE(dmg.neutered_indicator, '') AS "Neutered Status",  
-    COALESCE(
-         CASE 
-            WHEN dmg.weight = CAST(dmg.weight AS INT) THEN CAST(CAST(ROUND(dmg.weight, 0) AS INT) AS TEXT) 
-            ELSE dmg.weight 
-        END, 
-    '') AS "Weight (kg)",        
-    COALESCE(diag.best_response, '') AS "Response to Treatment",  
-    COALESCE(coh.cohort_description, '') AS "Cohort"  
-FROM 
-    df_case c
-JOIN 
-    df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
-JOIN 
-    df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
-JOIN 
-    df_diagnosis diag ON diag."case.case_record_id" = c.case_record_id
-JOIN 
-    df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
-JOIN 
-    df_program p ON st."program.program_acronym" = p.program_acronym
-JOIN 
-    df_sample smp ON smp."case.case_record_id" = c.case_record_id
-JOIN 
-    df_publication pub ON pub."study.clinical_study_designation" = st.clinical_study_designation
-LEFT JOIN 
-    df_case_file cf ON cf."sample.sample_id" = smp.sample_id
-LEFT JOIN 
-    df_study_file sf ON sf."study.clinical_study_designation" = st.clinical_study_designation
-LEFT JOIN
-   df_cohort coh ON coh.cohort_record_id= c."cohort.cohort_record_id"
-WHERE
-    st.clinical_study_designation = 'COTC021' AND cf."sample.sample_id" LIKE 'COTC021%'
-ORDER BY 
-    c.case_record_id ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT 
-    COUNT(DISTINCT p.program_acronym)              AS "Programs",
-    COUNT(DISTINCT st.clinical_study_designation)  AS "Studies",
-    COUNT(DISTINCT c.case_record_id)               AS "Cases",
-    COUNT(DISTINCT smp.sample_id)                  AS "Samples",
-    -- counts only case files that match the condition (but does not filter samples)
-    COUNT(DISTINCT CASE
-        WHEN cf."sample.sample_id" LIKE 'COTC021%' THEN cf.file_name
-    END)                                           AS "Case Files",
-    -- keep your original expression (though it's odd); see note below
-    CASE
-      WHEN EXISTS (SELECT 1 FROM df_study st2 WHERE st2.type = 'sample')
-      THEN (SELECT COUNT(*) FROM df_study st3 WHERE st3.type = 'sample')
-      ELSE 0
-    END                                            AS "Study Files"
-FROM df_program p
-JOIN df_study st
-  ON p.program_acronym = st."program.program_acronym"
-JOIN df_case c
-  ON st.clinical_study_designation = c."study.clinical_study_designation"
-JOIN df_demographic dmg
-  ON dmg."case.case_record_id" = c.case_record_id
-JOIN df_diagnosis diag
-  ON diag."case.case_record_id" = c.case_record_id
-LEFT JOIN df_sample smp
-  ON smp."case.case_record_id" = c.case_record_id
-LEFT JOIN df_case_file cf
-  ON cf."sample.sample_id" = smp.sample_id
-LEFT JOIN df_study_file sf
-  ON sf."study.clinical_study_designation" = st.clinical_study_designation
-WHERE st.clinical_study_designation = 'COTC021'
-  AND EXISTS (
-      SELECT 1
-      FROM df_sample s2
-      JOIN df_case_file cf2
-        ON cf2."sample.sample_id" = s2.sample_id
-      WHERE s2."case.case_record_id" = c.case_record_id
-        AND cf2."sample.sample_id" LIKE 'COTC021%'
-  );</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT
-    smp.sample_id AS "Sample ID",
-    c.case_record_id AS "Case ID",
-    COALESCE(dmg.breed, '') AS "Breed",
-    COALESCE(diag.disease_term, '') AS "Diagnosis",
-    COALESCE(smp.sample_site, '') AS "Sample Site",
-    COALESCE(smp.summarized_sample_type, '') AS "Sample Type",
-    COALESCE(smp.specific_sample_pathology, '') AS "Pathology/Morphology",
-    COALESCE(smp.tumor_grade, '') AS "Tumor Grade",
-    COALESCE(smp.sample_chronology, '') AS "Sample Chronology",
-    COALESCE(smp.percentage_tumor, '') AS "Percentage Tumor",
-    COALESCE(smp.necropsy_sample, '') AS "Necropsy Sample",
-    COALESCE(smp.sample_preservation, '') AS "Sample Preservation"
-FROM df_sample smp
-JOIN df_case c
-  ON smp."case.case_record_id" = c.case_record_id
-JOIN df_study st
-  ON c."study.clinical_study_designation" = st.clinical_study_designation
-JOIN df_program p
-  ON st."program.program_acronym" = p.program_acronym
-JOIN df_publication pub
-  ON pub."study.clinical_study_designation" = st.clinical_study_designation
-JOIN df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
-JOIN df_diagnosis diag  ON diag."case.case_record_id" = c.case_record_id
-JOIN df_enrollment enr  ON enr."case.case_record_id" = c.case_record_id
-LEFT JOIN df_case_file cf
-  ON cf."sample.sample_id" = smp.sample_id
-LEFT JOIN df_study_file sf
-  ON sf."study.clinical_study_designation" = st.clinical_study_designation
-WHERE st.clinical_study_designation = 'COTC021'
-  AND EXISTS (
-      SELECT 1
-      FROM df_sample s2
-      JOIN df_case_file cf2
-        ON cf2."sample.sample_id" = s2.sample_id
-      WHERE s2."case.case_record_id" = c.case_record_id
-        AND cf2."sample.sample_id" LIKE 'COTC021%'
-  )
-ORDER BY smp.sample_id ASC
 LIMIT 100;</t>
   </si>
   <si>
@@ -269,6 +228,7 @@
         WHEN cf.file_name LIKE '%.fastq.gz' THEN 'fastq'
         WHEN cf.file_name LIKE '%.vcf.gz' THEN 'vcf'
         WHEN cf.file_name LIKE '%.tsv.gz' THEN 'tsv'
+        WHEN cf.file_name LIKE '%.txt.gz' THEN 'txt'
         WHEN cf.file_name LIKE '%.pdf' THEN 'pdf'
         WHEN cf.file_name LIKE '%.rtf' THEN 'rtf'
         WHEN cf.file_name LIKE '%.tbi' THEN 'tbi'
@@ -318,7 +278,7 @@
 JOIN 
     df_sample smp ON cf."sample.sample_id" = smp.sample_id
 JOIN 
-    df_case c ON smp."case.case_record_id" = c.case_record_id
+    df_case c ON smp."case.case_id" = c.case_record_id
 JOIN 
     df_study st ON c."study.clinical_study_designation" = st.clinical_study_designation
 JOIN 
@@ -339,14 +299,61 @@
     cf.file_name ASC
 LIMIT 100;</t>
   </si>
+  <si>
+    <t xml:space="preserve"> SELECT
+    COUNT(DISTINCT p.program_acronym) AS "Programs",
+    COUNT(DISTINCT st.clinical_study_designation) AS "Studies",
+    COUNT(DISTINCT c.case_record_id) AS "Cases",
+    COUNT(DISTINCT smp.sample_id) AS "Samples",
+    COUNT(DISTINCT cf.file_name) AS "Case Files",         
+    CASE
+    when exists (select 1 from df_study st where st.type = 'sample') 
+then (select count (st.type) from df_study st where st.type = 'sample' )
+else 0
+    END AS 'Study Files'
+FROM 
+    df_program p
+JOIN 
+    df_study st ON p.program_acronym = st."program.program_acronym"
+JOIN 
+    df_case c ON st.clinical_study_designation = c."study.clinical_study_designation"
+JOIN 
+    df_demographic dmg ON dmg."case.case_record_id" = c.case_record_id
+JOIN 
+    df_diagnosis diag ON diag."case.case_record_id" = c.case_record_id
+JOIN 
+    df_enrollment enr ON enr."case.case_record_id" = c.case_record_id
+JOIN 
+    df_sample smp ON smp."case.case_record_id" = c.case_record_id
+LEFT JOIN 
+    df_case_file cf ON cf."sample.sample_id" = smp.sample_id 
+LEFT JOIN 
+    df_study_file sf ON sf."study.clinical_study_designation" = st.clinical_study_designation
+WHERE 
+    st.clinical_study_designation = 'COTC021' AND smp.type = 'sample';</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -406,11 +413,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -768,10 +781,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -785,7 +798,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -793,8 +806,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -803,7 +816,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -811,7 +824,7 @@
       <c r="C6" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
